--- a/output/pdf_financials_xlsx/CTZ.xlsx
+++ b/output/pdf_financials_xlsx/CTZ.xlsx
@@ -5688,13 +5688,13 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.191468</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.305642</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.331959</v>
       </c>
     </row>
     <row r="93">
@@ -9570,7 +9570,11 @@
           <t>Reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10226,7 +10230,11 @@
           <t>Reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CTZ.xlsx
+++ b/output/pdf_financials_xlsx/CTZ.xlsx
@@ -922,19 +922,19 @@
         <v>0.771889</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>1.163106</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>1.393475</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>1.545066</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>1.69735</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>1.931933</v>
       </c>
     </row>
     <row r="11">
@@ -1032,19 +1032,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.017121</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.005812</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.195112</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.29184</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.265771</v>
       </c>
     </row>
     <row r="13">
@@ -1967,19 +1967,19 @@
         <v>1.486016</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.725322</v>
+        <v>1.708201</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.898682</v>
+        <v>1.89287</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>2.296766</v>
+        <v>2.101654</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.889448</v>
+        <v>2.597608</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3.401302</v>
+        <v>3.135531</v>
       </c>
     </row>
     <row r="28">
@@ -2081,19 +2081,19 @@
         <v>1.491222</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.725322</v>
+        <v>1.708201</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.898682</v>
+        <v>1.89287</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.296766</v>
+        <v>2.101654</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.889448</v>
+        <v>2.597608</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.401302</v>
+        <v>3.135531</v>
       </c>
     </row>
     <row r="30">
@@ -2140,19 +2140,19 @@
         <v>45.99594148558654</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>34.67894695372662</v>
+        <v>34.33481510425461</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>35.19479289335379</v>
+        <v>35.08705914104762</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>37.69503464620172</v>
+        <v>34.49281308776272</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>42.24249014567818</v>
+        <v>37.97591454919237</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>43.10025653843547</v>
+        <v>39.73248787794118</v>
       </c>
     </row>
     <row r="31">
@@ -2287,52 +2287,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.013654</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.21927</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.050341</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.05602</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.033831</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.104536</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.206128</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.354666</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.627823</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.715598</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.935513</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.550039</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.708122</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.119089</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.8178</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.846423</v>
       </c>
     </row>
     <row r="35">
@@ -2397,52 +2397,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.013654</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.21927</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.050341</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.05602</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.033831</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.104536</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.206128</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.354666</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.627823</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.715598</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.935513</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>2.010899</v>
+        <v>4.560938</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.8</v>
+        <v>5.508122</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>6.099223</v>
+        <v>7.218312</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>7.229551</v>
+        <v>8.047351000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>9.329249000000001</v>
+        <v>10.175672</v>
       </c>
     </row>
     <row r="37">
@@ -3057,52 +3057,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.356802</v>
+        <v>0.343148</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.423859</v>
+        <v>0.204589</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.068207</v>
+        <v>0.017866</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.065124</v>
+        <v>0.009103999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.05819</v>
+        <v>0.024359</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.117748</v>
+        <v>0.013212</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.230226</v>
+        <v>0.024098</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.389773</v>
+        <v>0.035107</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.658965</v>
+        <v>0.031142</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.770848</v>
+        <v>0.05525</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.006995</v>
+        <v>0.071482</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.747395</v>
+        <v>0.197356</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.822792</v>
+        <v>0.11467</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.258139</v>
+        <v>0.13905</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.989693</v>
+        <v>0.171893</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.018775</v>
+        <v>0.172352</v>
       </c>
     </row>
     <row r="49">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -28684,7 +28684,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -28852,7 +28852,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -30416,7 +30416,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">

--- a/output/pdf_financials_xlsx/CTZ.xlsx
+++ b/output/pdf_financials_xlsx/CTZ.xlsx
@@ -2022,16 +2022,16 @@
         <v>0.005206</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.07466100000000001</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.022796</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.007191</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.007023</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
@@ -2081,16 +2081,16 @@
         <v>1.491222</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.708201</v>
+        <v>1.782862</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.89287</v>
+        <v>1.915666</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.101654</v>
+        <v>2.108845</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.597608</v>
+        <v>2.604631</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>3.135531</v>
@@ -2140,16 +2140,16 @@
         <v>45.99594148558654</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>34.33481510425461</v>
+        <v>35.83550011175592</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>35.08705914104762</v>
+        <v>35.50961568226773</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>34.49281308776272</v>
+        <v>34.61083337983463</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>37.97591454919237</v>
+        <v>38.07858779622541</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>39.73248787794118</v>
@@ -6102,16 +6102,16 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.07466100000000001</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.022796</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.007191</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.007023</v>
       </c>
       <c r="Q100" s="1" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.2469</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -17420,7 +17420,11 @@
           <t>Depreciation of property and equipment (Note 4)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -19340,7 +19344,11 @@
           <t>Depreciation of property and equipment (Note 4)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -19432,7 +19440,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -20538,7 +20550,11 @@
           <t>Depreciation of right-of-use asset (Note 17)</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -27402,7 +27418,11 @@
           <t>Issuance of common shares, net of issuance costs (Note 8 (a))</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -28072,7 +28092,11 @@
           <t>Issuance of common shares, net of issuance costs (Note 8)</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CTZ.xlsx
+++ b/output/pdf_financials_xlsx/CTZ.xlsx
@@ -1296,7 +1296,7 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.53</v>
+        <v>-0.53</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0.219</v>
@@ -2623,40 +2623,40 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.01944</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.000895</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.004245</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.00405</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.00424</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.026694</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.010718</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.091282</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.033003</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0</v>
@@ -2678,40 +2678,40 @@
         <v>0.07273</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.301552</v>
+        <v>0.320992</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.274337</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.126054</v>
+        <v>0.126949</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.15969</v>
+        <v>0.163935</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.239654</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.237583</v>
+        <v>0.241633</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.348416</v>
+        <v>0.352656</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.438942</v>
+        <v>0.465636</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.506831</v>
+        <v>0.517549</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0.605455</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.0388</v>
+        <v>1.130082</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1.181189</v>
+        <v>1.214192</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.975812</v>
@@ -3063,40 +3063,40 @@
         <v>0.204589</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.017866</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.009103999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.024359</v>
+        <v>0.023464</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.013212</v>
+        <v>0.008966999999999999</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.024098</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.035107</v>
+        <v>0.031057</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.031142</v>
+        <v>0.026902</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.05525</v>
+        <v>0.028556</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.071482</v>
+        <v>0.060764</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.197356</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.11467</v>
+        <v>0.023388</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.13905</v>
+        <v>0.106047</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.171893</v>
@@ -3562,16 +3562,16 @@
         <v>0</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>0.06918100000000001</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>0.06528200000000001</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>0.07026300000000001</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>0.07026300000000001</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>0</v>
@@ -3617,16 +3617,16 @@
         <v>0</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>0.032998</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>0.031816</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>0.039006</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>0</v>
+        <v>0.039006</v>
       </c>
       <c r="Q57" s="3" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.000833</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.011799</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -7313,10 +7313,10 @@
         <v>0</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-0.103423</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-0.339924</v>
       </c>
       <c r="Q121" s="1" t="inlineStr">
         <is>
@@ -17518,7 +17518,11 @@
           <t>Deferred income tax expense (Note 9)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -18716,7 +18720,11 @@
           <t>Share repurchases (Note 6)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19636,7 +19644,11 @@
           <t>Deferred income tax expense (Note 9)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -22104,7 +22116,11 @@
           <t>Deferred income tax expense (Note 10)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -23044,7 +23060,11 @@
           <t>Deferred income tax expense (recovery) (Note 12)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -23976,7 +23996,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -26466,7 +26490,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -26750,7 +26778,11 @@
           <t>Accretion expense (Note 6)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -34204,7 +34236,11 @@
           <t>DEFERRED INCOME TAX RECOVERY (Note 13)</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
